--- a/StructureDefinition-smart-slot.xlsx
+++ b/StructureDefinition-smart-slot.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$23</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T18:21:29+00:00</t>
+    <t>2026-03-02T13:43:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -573,7 +576,7 @@
     <t>The style of appointment or patient that may be booked in the slot (not service type).</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0276</t>
+    <t>https://smart-scheduling-links.org/ValueSet/appointment-type-and-reasons-vs</t>
   </si>
   <si>
     <t>Slot.schedule</t>
@@ -796,6 +799,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -997,7 +1015,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.28515625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="41.98046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -1131,7 +1149,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -1240,7 +1258,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>84</v>
       </c>
@@ -1351,7 +1369,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>92</v>
       </c>
@@ -1460,7 +1478,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>98</v>
       </c>
@@ -1571,7 +1589,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>104</v>
       </c>
@@ -1682,7 +1700,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>113</v>
       </c>
@@ -1793,7 +1811,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>121</v>
       </c>
@@ -1904,7 +1922,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>129</v>
       </c>
@@ -2011,7 +2029,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>137</v>
       </c>
@@ -2122,7 +2140,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>143</v>
       </c>
@@ -2233,7 +2251,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>148</v>
       </c>
@@ -2346,7 +2364,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>155</v>
       </c>
@@ -2455,7 +2473,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>160</v>
       </c>
@@ -2562,7 +2580,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>167</v>
       </c>
@@ -2669,7 +2687,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>171</v>
       </c>
@@ -2797,7 +2815,7 @@
         <v>85</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>20</v>
@@ -2885,7 +2903,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>180</v>
       </c>
@@ -2994,7 +3012,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>184</v>
       </c>
@@ -3103,7 +3121,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>191</v>
       </c>
@@ -3212,7 +3230,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>197</v>
       </c>
@@ -3321,7 +3339,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>201</v>
       </c>
@@ -3432,7 +3450,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>206</v>
       </c>
@@ -3542,6 +3560,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AM23">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI22">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-smart-slot.xlsx
+++ b/StructureDefinition-smart-slot.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T13:43:11+00:00</t>
+    <t>2026-03-02T13:46:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-smart-slot.xlsx
+++ b/StructureDefinition-smart-slot.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T13:46:35+00:00</t>
+    <t>2026-03-02T18:28:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
